--- a/데이터/opened_course2023_1.xlsx
+++ b/데이터/opened_course2023_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\AI융개_팀플\데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CAE796-656C-4CF9-8390-7BE88B897A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADEA366-0865-4416-AF10-4F747A5118D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5940" yWindow="5940" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="핵심전공2023_1" sheetId="3" r:id="rId1"/>
@@ -707,9 +707,6 @@
     <t>라이프스타일과 트렌드</t>
   </si>
   <si>
-    <t>서비스·디자인공학과</t>
-  </si>
-  <si>
     <t>정보설계와 시각화</t>
   </si>
   <si>
@@ -774,6 +771,10 @@
   </si>
   <si>
     <t>재무회계</t>
+  </si>
+  <si>
+    <t>서비스디자인공학과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1160,7 +1161,7 @@
   <dimension ref="A1:E105"/>
   <sheetFormatPr defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.15234375" customWidth="1"/>
+    <col min="1" max="1" width="23.23046875" customWidth="1"/>
     <col min="2" max="2" width="20.07421875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1183,10 +1184,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C2" t="s">
         <v>185</v>
@@ -1200,10 +1201,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C3" t="s">
         <v>185</v>
@@ -1217,10 +1218,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C4" t="s">
         <v>185</v>
@@ -1234,10 +1235,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C5" t="s">
         <v>185</v>
@@ -1251,10 +1252,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C6" t="s">
         <v>185</v>
@@ -1268,10 +1269,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C7" t="s">
         <v>185</v>
@@ -1285,10 +1286,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C8" t="s">
         <v>185</v>
@@ -1302,10 +1303,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C9" t="s">
         <v>185</v>
@@ -1319,10 +1320,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C10" t="s">
         <v>185</v>
@@ -1336,10 +1337,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C11" t="s">
         <v>185</v>
@@ -1353,10 +1354,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C12" t="s">
         <v>185</v>
@@ -1370,10 +1371,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C13" t="s">
         <v>185</v>
@@ -1387,10 +1388,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B14" t="s">
         <v>240</v>
-      </c>
-      <c r="B14" t="s">
-        <v>241</v>
       </c>
       <c r="C14" t="s">
         <v>185</v>
@@ -1404,10 +1405,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
+        <v>239</v>
+      </c>
+      <c r="B15" t="s">
         <v>240</v>
-      </c>
-      <c r="B15" t="s">
-        <v>241</v>
       </c>
       <c r="C15" t="s">
         <v>185</v>
@@ -1421,10 +1422,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s">
         <v>185</v>
@@ -1441,7 +1442,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C17" t="s">
         <v>185</v>
@@ -1458,7 +1459,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C18" t="s">
         <v>185</v>
@@ -1475,7 +1476,7 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C19" t="s">
         <v>185</v>
@@ -1492,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C20" t="s">
         <v>185</v>
@@ -1509,7 +1510,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C21" t="s">
         <v>185</v>
@@ -1526,7 +1527,7 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C22" t="s">
         <v>185</v>
@@ -1543,7 +1544,7 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C23" t="s">
         <v>185</v>
@@ -1560,7 +1561,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C24" t="s">
         <v>185</v>
@@ -1577,7 +1578,7 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C25" t="s">
         <v>185</v>
@@ -1594,7 +1595,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C26" t="s">
         <v>185</v>
@@ -1611,7 +1612,7 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C27" t="s">
         <v>185</v>
@@ -1628,7 +1629,7 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C28" t="s">
         <v>185</v>
@@ -1645,7 +1646,7 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C29" t="s">
         <v>185</v>
@@ -1662,7 +1663,7 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C30" t="s">
         <v>185</v>
@@ -1679,7 +1680,7 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C31" t="s">
         <v>185</v>
@@ -1696,7 +1697,7 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C32" t="s">
         <v>185</v>
@@ -1713,7 +1714,7 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C33" t="s">
         <v>185</v>
@@ -1730,7 +1731,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C34" t="s">
         <v>185</v>
@@ -1747,7 +1748,7 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C35" t="s">
         <v>185</v>
@@ -1764,7 +1765,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C36" t="s">
         <v>185</v>
@@ -1781,7 +1782,7 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C37" t="s">
         <v>185</v>
@@ -1798,7 +1799,7 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C38" t="s">
         <v>185</v>
@@ -1815,7 +1816,7 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" t="s">
         <v>185</v>
@@ -1832,7 +1833,7 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C40" t="s">
         <v>185</v>
@@ -1849,7 +1850,7 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C41" t="s">
         <v>185</v>
@@ -1866,7 +1867,7 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C42" t="s">
         <v>185</v>
@@ -1883,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C43" t="s">
         <v>185</v>
@@ -1900,7 +1901,7 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C44" t="s">
         <v>185</v>
@@ -1917,7 +1918,7 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C45" t="s">
         <v>185</v>
@@ -1934,7 +1935,7 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C46" t="s">
         <v>185</v>
@@ -1951,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C47" t="s">
         <v>185</v>
@@ -1968,7 +1969,7 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C48" t="s">
         <v>185</v>
@@ -1985,7 +1986,7 @@
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C49" t="s">
         <v>185</v>
@@ -2002,7 +2003,7 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C50" t="s">
         <v>185</v>
@@ -2019,7 +2020,7 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
         <v>185</v>
@@ -2036,7 +2037,7 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C52" t="s">
         <v>185</v>
@@ -2053,7 +2054,7 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C53" t="s">
         <v>185</v>
@@ -2067,10 +2068,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="B54" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C54" t="s">
         <v>185</v>
@@ -2084,10 +2085,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="B55" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C55" t="s">
         <v>185</v>
@@ -2101,7 +2102,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="B56" t="s">
         <v>186</v>
@@ -2118,7 +2119,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="B57" t="s">
         <v>186</v>
@@ -2135,10 +2136,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
+        <v>247</v>
+      </c>
+      <c r="B58" t="s">
         <v>225</v>
-      </c>
-      <c r="B58" t="s">
-        <v>226</v>
       </c>
       <c r="C58" t="s">
         <v>185</v>
@@ -2152,10 +2153,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
+        <v>247</v>
+      </c>
+      <c r="B59" t="s">
         <v>225</v>
-      </c>
-      <c r="B59" t="s">
-        <v>226</v>
       </c>
       <c r="C59" t="s">
         <v>185</v>
@@ -2169,7 +2170,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="B60" t="s">
         <v>224</v>
@@ -2186,7 +2187,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="B61" t="s">
         <v>224</v>
